--- a/data/trans_orig/IP38F_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP38F_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>44,22%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>41,23%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1449</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>442</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -833,97 +833,97 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>55,78%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>58,77%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,74 +1063,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3578</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4189</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1924</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5419</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>77,3%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>35,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4230</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>78,07%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>36,49%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3828</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5236</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>73,11%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>21,24%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>11</t>
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>55,18%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5419</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5419</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5419</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,74 +1406,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5546</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7590</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>73,07%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5935</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3404</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7181</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>82,65%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6818</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>81,87%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>49,52%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8116</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6529</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8497</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>76,83%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>23</t>
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>26,93%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3777</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3442</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>18,13%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7590</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7590</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7590</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7181</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7181</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7181</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,97 +1749,97 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1683</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1790</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>79,08%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>83,29%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1790</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1683</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1862,97 +1862,97 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20,92%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>16,71%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1975,72 +1975,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,64 +2092,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4016</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3067</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3308</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4012</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4016</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4016</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4016</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3067</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3067</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3067</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,64 +2435,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10690</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>9354</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>9525</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>12170</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10690</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>10690</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10690</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>9354</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>9354</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>9354</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,74 +2778,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6561</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>8386</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>5223</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>9174</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>91,41%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3097</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6761</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>87,28%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>45,81%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>6477</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>17</t>
@@ -2853,27 +2853,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,107 +2891,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3951</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3664</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>54,19%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>4264</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3781</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6561</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6561</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6561</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>9174</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>9174</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>9174</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,64 +3121,64 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6948</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>4267</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>4671</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>6636</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>6948</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>6948</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>6948</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>4267</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>4267</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>4267</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>40269</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>36010</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>41558</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>37450</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>33489</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>40057</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>89,43%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>79,97%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>42688</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>31567</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44091</t>
+          <t>37926</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>80137</t>
+          <t>75743</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>70902</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>83490</t>
+          <t>78667</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>5859</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>4428</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1821</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>8389</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>41869</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>41869</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>41869</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>41878</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>41878</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>41878</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>44477</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>44477</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44477</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>81653</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>81653</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>81653</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
